--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="130">
   <si>
     <t>title</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Frontend Developer (m/w/d)</t>
   </si>
   <si>
+    <t>Senior Frontend Engineer</t>
+  </si>
+  <si>
     <t>Frontend Engineer (Remote)</t>
   </si>
   <si>
@@ -73,12 +76,12 @@
     <t>Frontend Developer – HTML/CSS (Freelancer)</t>
   </si>
   <si>
+    <t>Front End Software Developer (JavaScript, React ) (Remote, Full-Time) [HR132]</t>
+  </si>
+  <si>
     <t>Frontend Developer (Freelancer)</t>
   </si>
   <si>
-    <t>Front End Software Developer (JavaScript, React ) (Remote, Full-Time) [HR132]</t>
-  </si>
-  <si>
     <t>Software Engineer - Frontend Development</t>
   </si>
   <si>
@@ -112,9 +115,6 @@
     <t>Frontend Engineer - Investments Team</t>
   </si>
   <si>
-    <t>Senior Frontend Engineer</t>
-  </si>
-  <si>
     <t>React Developer</t>
   </si>
   <si>
@@ -190,6 +190,9 @@
     <t>Best Job Tool</t>
   </si>
   <si>
+    <t>mula.</t>
+  </si>
+  <si>
     <t>North Star Staffing</t>
   </si>
   <si>
@@ -349,6 +352,9 @@
     <t>Germany</t>
   </si>
   <si>
+    <t>Berlin, Berlin, Germany</t>
+  </si>
+  <si>
     <t>Bengaluru, Karnataka, India</t>
   </si>
   <si>
@@ -380,9 +386,6 @@
   </si>
   <si>
     <t>Hamburg, Germany</t>
-  </si>
-  <si>
-    <t>Berlin, Berlin, Germany</t>
   </si>
   <si>
     <t>Ireland</t>
@@ -732,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -760,14 +763,14 @@
         <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2">
-        <f>HYPERLINK("https://www.linkedin.com/jobs/view/frontend-typescript-developer-at-alignerr-4382641763?position=1&amp;pageNum=0&amp;refId=evwbrUIlLv2hmGMcC83pVw%3D%3D&amp;trackingId=kWvHA4ngdNJ9Ysf4pCeLkw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://www.linkedin.com/jobs/view/frontend-typescript-developer-at-alignerr-4382641763?position=1&amp;pageNum=0&amp;refId=lvLprFuPEOxKxyAHVCEzWQ%3D%3D&amp;trackingId=IAmz5eBj%2FLEuZbzdzNBkNg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -778,14 +781,14 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3">
-        <f>HYPERLINK("https://www.linkedin.com/jobs/view/frontend-engineer-at-dynamism-4382946658?position=5&amp;pageNum=0&amp;refId=evwbrUIlLv2hmGMcC83pVw%3D%3D&amp;trackingId=7gME46jer6jMF1ullwAoQQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://www.linkedin.com/jobs/view/frontend-engineer-at-dynamism-4382946658?position=2&amp;pageNum=0&amp;refId=lvLprFuPEOxKxyAHVCEzWQ%3D%3D&amp;trackingId=IJOiSqzigIdkp7TjSItezQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -796,14 +799,14 @@
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-software-engineer-remote-at-taskify-ai-4382929800?position=8&amp;pageNum=0&amp;refId=evwbrUIlLv2hmGMcC83pVw%3D%3D&amp;trackingId=07CtgaOJ4rB1QFKZeF96%2BQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-software-engineer-remote-at-taskify-ai-4382929800?position=7&amp;pageNum=0&amp;refId=lvLprFuPEOxKxyAHVCEzWQ%3D%3D&amp;trackingId=VetDzvnul0z2DN7pE0UZ3w%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -814,14 +817,14 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5">
-        <f>HYPERLINK("https://www.linkedin.com/jobs/view/frontend-software-engineer-remote-at-nexus-consulting-4382950212?position=10&amp;pageNum=0&amp;refId=evwbrUIlLv2hmGMcC83pVw%3D%3D&amp;trackingId=l1%2FAgFWmDjMO9hdnNSDJMg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://www.linkedin.com/jobs/view/frontend-software-engineer-remote-at-nexus-consulting-4382950212?position=10&amp;pageNum=0&amp;refId=lvLprFuPEOxKxyAHVCEzWQ%3D%3D&amp;trackingId=FZmnNOFuk7VmQTMjraijPg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -832,14 +835,14 @@
         <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-ambyint-4382372082?position=1&amp;pageNum=0&amp;refId=FywGc33CLPPQ7ibGSjfrWw%3D%3D&amp;trackingId=%2B7PftH4NNvSKDdHvH7yMDQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-ambyint-4382372082?position=1&amp;pageNum=0&amp;refId=DCPIieYFGXjPgXwJYkIwKw%3D%3D&amp;trackingId=9MVzAFxbZsTdJPqVzMWJwg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -850,14 +853,14 @@
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-havas-cx-canada-4382116206?position=3&amp;pageNum=0&amp;refId=FywGc33CLPPQ7ibGSjfrWw%3D%3D&amp;trackingId=bqXDf1QnHHkuRpFqduDbGg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-havas-cx-canada-4382116206?position=3&amp;pageNum=0&amp;refId=DCPIieYFGXjPgXwJYkIwKw%3D%3D&amp;trackingId=cE3mFWQC4eGcp%2BO7op9cOw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -868,14 +871,14 @@
         <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D8">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-micromart-4381085213?position=6&amp;pageNum=0&amp;refId=FywGc33CLPPQ7ibGSjfrWw%3D%3D&amp;trackingId=TVuEkEWvVk5TcYvmeXdo5g%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-micromart-4381085213?position=6&amp;pageNum=0&amp;refId=DCPIieYFGXjPgXwJYkIwKw%3D%3D&amp;trackingId=xN%2Fu4kQyNLFQq5S%2BfSU7dw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -886,14 +889,14 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-tata-consultancy-services-4381051246?position=10&amp;pageNum=0&amp;refId=FywGc33CLPPQ7ibGSjfrWw%3D%3D&amp;trackingId=asUZwFdSCxrYsu9rN%2BOBow%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-tata-consultancy-services-4381051246?position=10&amp;pageNum=0&amp;refId=DCPIieYFGXjPgXwJYkIwKw%3D%3D&amp;trackingId=586GCW65QYwKwBxyelv2vQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -904,14 +907,14 @@
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-m-w-d-at-itb-gmbh-4382689177?position=2&amp;pageNum=0&amp;refId=o3FBXhidiGyLGcl1iLW1wg%3D%3D&amp;trackingId=NUdClP4GItfOg3a2OXtiBg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-m-w-d-at-itb-gmbh-4382689177?position=2&amp;pageNum=0&amp;refId=OgdcAYSekNi2z6qbDOl8VA%3D%3D&amp;trackingId=ifaCK4ZRK2Ugf8DRFSE7ww%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -922,14 +925,14 @@
         <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-at-fetchjobs-co-4381582490?position=3&amp;pageNum=0&amp;refId=o3FBXhidiGyLGcl1iLW1wg%3D%3D&amp;trackingId=JXbRXIUSCktsIX2B%2B8So5w%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-at-fetchjobs-co-4381582490?position=3&amp;pageNum=0&amp;refId=OgdcAYSekNi2z6qbDOl8VA%3D%3D&amp;trackingId=1l6jD06pVakuhGtjFsl1UA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -940,14 +943,14 @@
         <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-at-best-job-tool-4382936306?position=4&amp;pageNum=0&amp;refId=o3FBXhidiGyLGcl1iLW1wg%3D%3D&amp;trackingId=B1ZYgYT1fDaXMJvI%2BfSsjQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-at-best-job-tool-4382936306?position=4&amp;pageNum=0&amp;refId=OgdcAYSekNi2z6qbDOl8VA%3D%3D&amp;trackingId=vsCgS2LNxOosnCxCXoQjaQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -958,14 +961,14 @@
         <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D13">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-engineer-remote-at-north-star-staffing-4382939925?position=6&amp;pageNum=0&amp;refId=o3FBXhidiGyLGcl1iLW1wg%3D%3D&amp;trackingId=1pRQF59XAe4el4MxbYHOrg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/senior-frontend-engineer-at-mula-4381700999?position=5&amp;pageNum=0&amp;refId=OgdcAYSekNi2z6qbDOl8VA%3D%3D&amp;trackingId=YdKIHaV%2FzIAMZUx%2FgIFCDg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -976,14 +979,14 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D14">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/full-stack-developer-javascript-at-jobgether-4382902539?position=8&amp;pageNum=0&amp;refId=o3FBXhidiGyLGcl1iLW1wg%3D%3D&amp;trackingId=WhBTVRR3iFXy81nm8VkGLg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-engineer-remote-at-north-star-staffing-4382939925?position=7&amp;pageNum=0&amp;refId=OgdcAYSekNi2z6qbDOl8VA%3D%3D&amp;trackingId=jwoYjeg0PF25Sb46QtAp0Q%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -997,11 +1000,11 @@
         <v>111</v>
       </c>
       <c r="D15">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/sde-1-frontend-web-at-licious-4381004417?position=2&amp;pageNum=0&amp;refId=nmBlGcqjgIczsecgKS380w%3D%3D&amp;trackingId=22USOZSbPFIkpTRkx8zP1Q%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/full-stack-developer-javascript-at-jobgether-4382902539?position=9&amp;pageNum=0&amp;refId=OgdcAYSekNi2z6qbDOl8VA%3D%3D&amp;trackingId=HtVMcFLefFnI06t1j%2BVf%2BA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1012,14 +1015,14 @@
         <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D16">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-%E2%80%93-front-end-javascript-typescript-%E2%80%93-react-angular-bangalore-5%E2%80%938-years-at-cisco-4380979913?position=3&amp;pageNum=0&amp;refId=nmBlGcqjgIczsecgKS380w%3D%3D&amp;trackingId=IAo6glLcou%2FU3aozAQSAjw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/sde-1-frontend-web-at-licious-4381004417?position=2&amp;pageNum=0&amp;refId=Bi%2FpG9oDmtZSDeezHTEV8w%3D%3D&amp;trackingId=KN5X71HsK3vrUEVrfwHpqw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1030,14 +1033,14 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D17">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-ii-frontend-at-uber-4382952295?position=4&amp;pageNum=0&amp;refId=nmBlGcqjgIczsecgKS380w%3D%3D&amp;trackingId=9iMKYp7zcltbDzXJ7J%2BypA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-%E2%80%93-front-end-javascript-typescript-%E2%80%93-react-angular-bangalore-5%E2%80%938-years-at-cisco-4380979913?position=3&amp;pageNum=0&amp;refId=Bi%2FpG9oDmtZSDeezHTEV8w%3D%3D&amp;trackingId=Ed9C%2Fx%2FMTWdv0q%2F7NhU%2BWw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1048,14 +1051,14 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-sde-1-at-limechat-4379862161?position=7&amp;pageNum=0&amp;refId=nmBlGcqjgIczsecgKS380w%3D%3D&amp;trackingId=2Of2u3alAw1zc%2FTPizv2mw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-ii-frontend-at-uber-4382952295?position=4&amp;pageNum=0&amp;refId=Bi%2FpG9oDmtZSDeezHTEV8w%3D%3D&amp;trackingId=Mqa%2B%2FNy3fPJ3kSZuIh%2FN2w%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1066,14 +1069,14 @@
         <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D19">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-intern-at-skillovilla-4381027138?position=10&amp;pageNum=0&amp;refId=nmBlGcqjgIczsecgKS380w%3D%3D&amp;trackingId=oUJIfiVV1%2Bclj11BZ4%2FzUw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-sde-1-at-limechat-4379862161?position=7&amp;pageNum=0&amp;refId=Bi%2FpG9oDmtZSDeezHTEV8w%3D%3D&amp;trackingId=BNo9bs%2BtXNGF8qw7UZAlvA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1084,14 +1087,14 @@
         <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-frontend-at-paypal-4348410085?position=1&amp;pageNum=0&amp;refId=7yQ6D9e%2F02QpB2X1kDvmMg%3D%3D&amp;trackingId=n1hF%2BlwW47V%2F7tigHfXKiQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-intern-at-skillovilla-4381027138?position=10&amp;pageNum=0&amp;refId=Bi%2FpG9oDmtZSDeezHTEV8w%3D%3D&amp;trackingId=k8YQGIq3d7KfGqZ8Irx%2F9A%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1102,32 +1105,32 @@
         <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D21">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-%E2%80%93-html-css-freelancer-at-deccan-ai-experts-4380354385?position=4&amp;pageNum=0&amp;refId=7yQ6D9e%2F02QpB2X1kDvmMg%3D%3D&amp;trackingId=Fw%2BcdvnyXd7HkcuEIOHxAw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-frontend-at-paypal-4348410085?position=1&amp;pageNum=0&amp;refId=R2Pn0iJVFLt0Or1MZ6JEqg%3D%3D&amp;trackingId=6fi28IM3oGTD4SqF2p%2FuNw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D22">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-%E2%80%93-html-css-freelancer-at-deccan-ai-experts-4380337616?position=6&amp;pageNum=0&amp;refId=%2B2JMeKiLvq9W8O3lq1Ds4A%3D%3D&amp;trackingId=w5Pi6JcEWG4OnfCpWozBUA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-%E2%80%93-html-css-freelancer-at-deccan-ai-experts-4380354385?position=4&amp;pageNum=0&amp;refId=R2Pn0iJVFLt0Or1MZ6JEqg%3D%3D&amp;trackingId=3dbc8Mh7Qp63xVf1S22jVg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1135,17 +1138,17 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D23">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-freelancer-at-deccan-ai-experts-4380943681?position=2&amp;pageNum=0&amp;refId=jwONt948FIMYg8WkRu%2FL5g%3D%3D&amp;trackingId=w1URoq9df82pb63Q2gv57w%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-%E2%80%93-html-css-freelancer-at-deccan-ai-experts-4380337616?position=6&amp;pageNum=0&amp;refId=XRYvNb3gPZTtiO72QHjQHQ%3D%3D&amp;trackingId=jVmjq8rZzpBZ0hm%2Bmwg4dw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1153,53 +1156,53 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D24">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/front-end-software-developer-javascript-react-remote-full-time-hr132-at-smart-working-4380240510?position=6&amp;pageNum=0&amp;refId=jwONt948FIMYg8WkRu%2FL5g%3D%3D&amp;trackingId=Cnxj8acnh8qKyILBS7XDfQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/front-end-software-developer-javascript-react-remote-full-time-hr132-at-smart-working-4380240510?position=2&amp;pageNum=0&amp;refId=dGm7%2FUoajPaPh%2BfnhSyF4g%3D%3D&amp;trackingId=6Qvlt%2BgXOH4%2FlSNpfGRk6Q%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D25">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-graystone-capital-mena-4381256421?position=7&amp;pageNum=0&amp;refId=jwONt948FIMYg8WkRu%2FL5g%3D%3D&amp;trackingId=1TnExsFU3dL3lmaFLJj5Pg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-freelancer-at-deccan-ai-experts-4380943681?position=3&amp;pageNum=0&amp;refId=dGm7%2FUoajPaPh%2BfnhSyF4g%3D%3D&amp;trackingId=WPIZzfsSPuBJVwjEBg9FwA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D26">
-        <f>HYPERLINK("https://www.linkedin.com/jobs/view/software-engineer-frontend-development-at-metron-inc-4379961813?position=2&amp;pageNum=0&amp;refId=pQEa%2FDJ04cWGqVOLExI5oQ%3D%3D&amp;trackingId=3N6MV9Y%2Bqd016Ve6scPNgQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-graystone-capital-mena-4381256421?position=7&amp;pageNum=0&amp;refId=dGm7%2FUoajPaPh%2BfnhSyF4g%3D%3D&amp;trackingId=43vJ4uAuPFSGUlh1BXvPMg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1210,86 +1213,86 @@
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D27">
-        <f>HYPERLINK("https://www.linkedin.com/jobs/view/react-front-end-developer-966-at-sharp-decisions-4380362564?position=6&amp;pageNum=0&amp;refId=pQEa%2FDJ04cWGqVOLExI5oQ%3D%3D&amp;trackingId=Ly6OUuHg%2FHeItPw2WAJ24A%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://www.linkedin.com/jobs/view/software-engineer-frontend-development-at-metron-inc-4379961813?position=3&amp;pageNum=0&amp;refId=DpZ9FtcjVf8MXmSaKAlveQ%3D%3D&amp;trackingId=11SYgq4bIoIogbrkb5rkpg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="D28">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-tiu-consulting-4380386019?position=2&amp;pageNum=0&amp;refId=mF5TDUkkm8yKKAR6rr87UQ%3D%3D&amp;trackingId=hu3gNQdnayyjNZv%2Fj%2BcRsA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://www.linkedin.com/jobs/view/react-front-end-developer-966-at-sharp-decisions-4380362564?position=7&amp;pageNum=0&amp;refId=DpZ9FtcjVf8MXmSaKAlveQ%3D%3D&amp;trackingId=7zzX7OY847DLfeWous2%2FXQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
         <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D29">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/react-javascript-engineer-frontend-remote-at-crossing-hurdles-4379170581?position=4&amp;pageNum=0&amp;refId=mF5TDUkkm8yKKAR6rr87UQ%3D%3D&amp;trackingId=jN9zXrAQ0hvJc%2BEUQPX57w%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-tiu-consulting-4380386019?position=2&amp;pageNum=0&amp;refId=lw4ysPd5vF9mX949nCnMQg%3D%3D&amp;trackingId=s9NfvQDOGpbYeQoHqAfk2A%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
         <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D30">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-bet99-4323386044?position=6&amp;pageNum=0&amp;refId=mF5TDUkkm8yKKAR6rr87UQ%3D%3D&amp;trackingId=8YtwTLidTnDiq4ni4ClLYw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/react-javascript-engineer-frontend-remote-at-crossing-hurdles-4379170581?position=4&amp;pageNum=0&amp;refId=lw4ysPd5vF9mX949nCnMQg%3D%3D&amp;trackingId=SMj2DNVtCaQrwrKvZ2PwnQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
         <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D31">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-engineer-react-js-at-deel-4370716292?position=9&amp;pageNum=0&amp;refId=mF5TDUkkm8yKKAR6rr87UQ%3D%3D&amp;trackingId=9502H1lFfP%2FCVNNCJwVMcg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-developer-at-bet99-4323386044?position=6&amp;pageNum=0&amp;refId=lw4ysPd5vF9mX949nCnMQg%3D%3D&amp;trackingId=TueWpQuAXJFu2aL15Yrhtg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1300,14 +1303,14 @@
         <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D32">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-frontend-engineer-m-w-d-at-evernest-4380872331?position=1&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=nvtIoWvk2yZarrkdPCIWcQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-engineer-react-js-at-deel-4370716292?position=9&amp;pageNum=0&amp;refId=lw4ysPd5vF9mX949nCnMQg%3D%3D&amp;trackingId=oM7J6UiNFFWjvbG5%2Fv9ATg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1318,14 +1321,14 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D33">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-frontend-developer-m-w-d-%E2%80%93-fokus-ai-ui-ux-at-weissenberg-group-4380838862?position=2&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=PH6wglh6nkHNo5yAELL82A%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-frontend-engineer-m-w-d-at-evernest-4380872331?position=1&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=yIEze4Lo4L%2FjXwx4Swm%2BIQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1336,14 +1339,14 @@
         <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D34">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-m-f-at-neuffer-fenster-%2B-t%C3%BCren-gmbh-4378593355?position=3&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=gtoko7jNmxm0wsUi5L%2F6og%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-frontend-developer-m-w-d-%E2%80%93-fokus-ai-ui-ux-at-weissenberg-group-4380838862?position=2&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=BvS%2FFc9Z8CMso1w2LrbaTA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1354,68 +1357,68 @@
         <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D35">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-engineer-m-w-d-berlin-at-code-compass-%F0%9F%A7%AD-4380279491?position=4&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=nzEnN6xBKhKVnY1Eu4bRMw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-m-f-at-neuffer-fenster-%2B-t%C3%BCren-gmbh-4378593355?position=3&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=9XrC4OM4mIAn0hicvg%2FYrw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
         <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D36">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-at-sr2-socially-responsible-recruitment-certified-b-corporation%E2%84%A2-4379866635?position=5&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=ozB6twhhTgellB3Q1CdmxQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-engineer-m-w-d-berlin-at-code-compass-%F0%9F%A7%AD-4380279491?position=4&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=2NyzGVzZ6KTqKatiZxa9Gg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D37">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-frontend-engineer-m-w-d-at-evernest-4380286755?position=6&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=dta3GsY2xFrw5%2F0y1lVIiw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-at-sr2-socially-responsible-recruitment-certified-b-corporation%E2%84%A2-4379866635?position=5&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=P47w83%2BjaDJDkkz75OVAQA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D38">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/senior-frontend-engineer-reactjs-m-f-d-at-join-4372898713?position=7&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=TgYpmQGC0q3GKxnGT4SLwg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-frontend-engineer-m-w-d-at-evernest-4380286755?position=6&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=FayjiKIfC7CFd%2B5oeBMvXg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1426,14 +1429,14 @@
         <v>81</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D39">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-inter-at-jhc-consulting-4380900687?position=10&amp;pageNum=0&amp;refId=RmiG1CL0d4PB7Ae%2FMleTxA%3D%3D&amp;trackingId=0ftRtbZUm5BmJcTOGLV4UQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/senior-frontend-engineer-reactjs-m-f-d-at-join-4372898713?position=7&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=5U5%2BVynQkEhIaGzu4Xi%2Fdg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1444,19 +1447,19 @@
         <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D40">
-        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/frontend-engineer-investments-team-at-kota-4382146803?position=1&amp;pageNum=0&amp;refId=D5l3mjkhN6QL0mmqKaVBdg%3D%3D&amp;trackingId=QK3TUF6%2BEtF%2BnnDUbNvzXA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-developer-inter-at-jhc-consulting-4380900687?position=10&amp;pageNum=0&amp;refId=bDw%2BUmO96kMRVHLJOjWF5w%3D%3D&amp;trackingId=MQnPQYDOhX0x6F1DX2muKA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
         <v>83</v>
@@ -1465,11 +1468,11 @@
         <v>124</v>
       </c>
       <c r="D41">
-        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/frontend-developer-at-ryanair-europe-s-favourite-airline-4309849710?position=2&amp;pageNum=0&amp;refId=D5l3mjkhN6QL0mmqKaVBdg%3D%3D&amp;trackingId=RkBnWe7%2BOYgKObqJ8aM8KQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/frontend-engineer-investments-team-at-kota-4382146803?position=1&amp;pageNum=0&amp;refId=ynIrtJdgApgSzX13DIy0mg%3D%3D&amp;trackingId=G%2F9LE7K3nDOOG5rfSjFMnw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1483,430 +1486,430 @@
         <v>125</v>
       </c>
       <c r="D42">
-        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/frontend-developer-at-comtrade-360-4378504404?position=3&amp;pageNum=0&amp;refId=D5l3mjkhN6QL0mmqKaVBdg%3D%3D&amp;trackingId=x1KZtiN2qssANdbGVS7tJQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/frontend-developer-at-ryanair-europe-s-favourite-airline-4309849710?position=2&amp;pageNum=0&amp;refId=ynIrtJdgApgSzX13DIy0mg%3D%3D&amp;trackingId=spcqUYmDBeqJ1IsjoFDGcQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D43">
-        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/full-stack-developer-javascript-at-jobgether-4382901607?position=4&amp;pageNum=0&amp;refId=D5l3mjkhN6QL0mmqKaVBdg%3D%3D&amp;trackingId=cEkTFbDY4gwy7O59UViHDw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/full-stack-developer-javascript-at-jobgether-4382901607?position=3&amp;pageNum=0&amp;refId=ynIrtJdgApgSzX13DIy0mg%3D%3D&amp;trackingId=CT24XT9rIP3QFpqccEuXuw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
         <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D44">
-        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/senior-frontend-engineer-at-stripe-4371513544?position=5&amp;pageNum=0&amp;refId=D5l3mjkhN6QL0mmqKaVBdg%3D%3D&amp;trackingId=8wH6I11rcDT3Wb3Kyvosvw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/frontend-developer-at-comtrade-360-4378504404?position=4&amp;pageNum=0&amp;refId=ynIrtJdgApgSzX13DIy0mg%3D%3D&amp;trackingId=IG7XjNHXX6oxKfaZuxAM8w%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D45">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-frontend-at-paypal-4364444879?position=1&amp;pageNum=0&amp;refId=JnGWMt1qxafICBLeiswxRw%3D%3D&amp;trackingId=em%2BcmLKobi%2BfIRu8gAvplQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ie.linkedin.com/jobs/view/senior-frontend-engineer-at-stripe-4371513544?position=5&amp;pageNum=0&amp;refId=ynIrtJdgApgSzX13DIy0mg%3D%3D&amp;trackingId=%2FK9hk1kP71gdk7hqarKcew%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D46">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-developer-at-persistent-systems-4309459084?position=4&amp;pageNum=0&amp;refId=JnGWMt1qxafICBLeiswxRw%3D%3D&amp;trackingId=P2%2F5Rujd2MHCE%2FRr7Um4EQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/software-engineer-frontend-at-paypal-4364444879?position=1&amp;pageNum=0&amp;refId=HKuTA3IXAnbo1%2B%2FcYssVuQ%3D%3D&amp;trackingId=rr9XxGxM%2BQuufpKErJui0g%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
         <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D47">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-software-engineer-frontend-at-roku-4312974061?position=6&amp;pageNum=0&amp;refId=JnGWMt1qxafICBLeiswxRw%3D%3D&amp;trackingId=Xi07OzRYuZOMQ74nhvC7uQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-developer-at-persistent-systems-4309459084?position=4&amp;pageNum=0&amp;refId=HKuTA3IXAnbo1%2B%2FcYssVuQ%3D%3D&amp;trackingId=64h20EXPmEBCPhXO%2FLHmfw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B48" t="s">
         <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D48">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-frontend-engineer-periscope-at-mckinsey-company-4382963014?position=9&amp;pageNum=0&amp;refId=JnGWMt1qxafICBLeiswxRw%3D%3D&amp;trackingId=V52h1p5fEDbbDxlIXV3nfQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-software-engineer-frontend-at-roku-4312974061?position=6&amp;pageNum=0&amp;refId=HKuTA3IXAnbo1%2B%2FcYssVuQ%3D%3D&amp;trackingId=MQ8xEzEcNY6yDLBfnkPUkw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
         <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D49">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-intern-at-weboin-digital-marketing-agency-4379196226?position=3&amp;pageNum=0&amp;refId=ky5xw5xG3XvJiwFa1ka%2FBw%3D%3D&amp;trackingId=fg%2FA8zXuXidx%2FRV7va5eEw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-frontend-engineer-periscope-at-mckinsey-company-4382963014?position=9&amp;pageNum=0&amp;refId=HKuTA3IXAnbo1%2B%2FcYssVuQ%3D%3D&amp;trackingId=6KhYaJQvTQzRjiTi9PfPlQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B50" t="s">
         <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D50">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-scoutit-4381521192?position=5&amp;pageNum=0&amp;refId=ky5xw5xG3XvJiwFa1ka%2FBw%3D%3D&amp;trackingId=hxwZWu7740BEXu632DA6eA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-intern-at-weboin-digital-marketing-agency-4379196226?position=3&amp;pageNum=0&amp;refId=vFa%2BuGCq4%2FNpp7TSXio4lQ%3D%3D&amp;trackingId=mxpvVnj4kD4L1fWixN%2FLgQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D51">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-software-engineer-frontend-at-paypal-4279474942?position=7&amp;pageNum=0&amp;refId=ky5xw5xG3XvJiwFa1ka%2FBw%3D%3D&amp;trackingId=80y5es0uzxlGjthROD28PA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-scoutit-4381521192?position=4&amp;pageNum=0&amp;refId=vFa%2BuGCq4%2FNpp7TSXio4lQ%3D%3D&amp;trackingId=fAGtY%2BVsjVtlVsz9guv%2BTQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D52">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-at-teceze-4381546887?position=9&amp;pageNum=0&amp;refId=ky5xw5xG3XvJiwFa1ka%2FBw%3D%3D&amp;trackingId=hO9s8OJqBcIxaSBkWGZ8pQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/senior-software-engineer-frontend-at-paypal-4279474942?position=7&amp;pageNum=0&amp;refId=vFa%2BuGCq4%2FNpp7TSXio4lQ%3D%3D&amp;trackingId=e61w7z0bSefkV%2B2i0HPTXQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" t="s">
         <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D53">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/junior-javascript-developer-remote-work-at-bairesdev-4378821972?position=10&amp;pageNum=0&amp;refId=ky5xw5xG3XvJiwFa1ka%2FBw%3D%3D&amp;trackingId=21gxwUyoGdWzHxmtZ8WKrg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-at-teceze-4381546887?position=9&amp;pageNum=0&amp;refId=vFa%2BuGCq4%2FNpp7TSXio4lQ%3D%3D&amp;trackingId=X8hDwH%2BSvUDYpJdrpRMjaw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D54">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-scoutit-4381514620?position=2&amp;pageNum=0&amp;refId=fqcqewy5QbPEFluDjZxHEQ%3D%3D&amp;trackingId=wTRpWp8vJnSeNW0jK5orDw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/junior-javascript-developer-remote-work-at-bairesdev-4378821972?position=10&amp;pageNum=0&amp;refId=vFa%2BuGCq4%2FNpp7TSXio4lQ%3D%3D&amp;trackingId=oBLOei6ute6O0zwXVIsFyA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D55">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/front-end-software-developer-javascript-react-remote-full-time-hr132-at-smart-working-4380234605?position=3&amp;pageNum=0&amp;refId=fqcqewy5QbPEFluDjZxHEQ%3D%3D&amp;trackingId=89QbWWJwU41AyWqyg3bT2Q%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-scoutit-4381514620?position=2&amp;pageNum=0&amp;refId=A6FwNIShtoTwha0SOMmohw%3D%3D&amp;trackingId=5U4pZp3RnPGsWQfEUwNK1Q%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D56">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-wenger-watson-4381567064?position=4&amp;pageNum=0&amp;refId=fqcqewy5QbPEFluDjZxHEQ%3D%3D&amp;trackingId=xqxINwaPNq0ZRYfDF0dH6w%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/front-end-software-developer-javascript-react-remote-full-time-hr132-at-smart-working-4380234605?position=3&amp;pageNum=0&amp;refId=A6FwNIShtoTwha0SOMmohw%3D%3D&amp;trackingId=q62nlfJPOmvRes6OIXNHAg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
         <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D57">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-developer-at-katalyst-cro-4381961262?position=9&amp;pageNum=0&amp;refId=fqcqewy5QbPEFluDjZxHEQ%3D%3D&amp;trackingId=sgN6FwTjQ6NaiYuZ25X2Bw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-at-wenger-watson-4381567064?position=4&amp;pageNum=0&amp;refId=A6FwNIShtoTwha0SOMmohw%3D%3D&amp;trackingId=UKD2%2FxBJDotgG4AhkxkMyg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
         <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D58">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-in-hyderabad-at-educase-india-4382192999?position=10&amp;pageNum=0&amp;refId=fqcqewy5QbPEFluDjZxHEQ%3D%3D&amp;trackingId=HitqFDvdkUVKBjmEmPdf0w%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-developer-at-katalyst-cro-4381961262?position=9&amp;pageNum=0&amp;refId=A6FwNIShtoTwha0SOMmohw%3D%3D&amp;trackingId=B1%2FKv%2B0pnaVXuQjFxecfaQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
         <v>96</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D59">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-in-ahmedabad-at-chaintech-network-4380588778?position=3&amp;pageNum=0&amp;refId=tO8ZQPpA16ZOsNP64DEmXg%3D%3D&amp;trackingId=daaGTjOOdwTXfSkqOCHaig%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-in-hyderabad-at-educase-india-4382192999?position=10&amp;pageNum=0&amp;refId=A6FwNIShtoTwha0SOMmohw%3D%3D&amp;trackingId=QD0o0GgV1l0McXdaRHkMpg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D60">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/reactjs-development-internship-in-ahmedabad-at-chaintech-network-4380706032?position=7&amp;pageNum=0&amp;refId=tO8ZQPpA16ZOsNP64DEmXg%3D%3D&amp;trackingId=97wk3hT5QpLJ%2FI6MTxJIsw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/react-js-developer-in-ahmedabad-at-chaintech-network-4380588778?position=3&amp;pageNum=0&amp;refId=%2BRvL2ZGxx1ioN5%2Fos2VrJA%3D%3D&amp;trackingId=CTS9FZ%2FZJaxPAlsz6x1TkA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D61">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/front-end-engineer-vue-js-react-js-remote-full-time-is004-at-smart-working-4377766395?position=8&amp;pageNum=0&amp;refId=tO8ZQPpA16ZOsNP64DEmXg%3D%3D&amp;trackingId=p%2BEFkLBy6hkwnjFYv%2F%2FjDg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/reactjs-development-internship-in-ahmedabad-at-chaintech-network-4380706032?position=7&amp;pageNum=0&amp;refId=%2BRvL2ZGxx1ioN5%2Fos2VrJA%3D%3D&amp;trackingId=6SzOCzOMm74hQpAQnAPsrg%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D62">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/full-stack-developer-react-js-node-js-at-e2logy-software-solutions-4379171718?position=9&amp;pageNum=0&amp;refId=tO8ZQPpA16ZOsNP64DEmXg%3D%3D&amp;trackingId=LUp8muSXRS0h8cSIxDDNYA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/front-end-engineer-vue-js-react-js-remote-full-time-is004-at-smart-working-4377766395?position=8&amp;pageNum=0&amp;refId=%2BRvL2ZGxx1ioN5%2Fos2VrJA%3D%3D&amp;trackingId=3LF8jUPZKJeo5yzT8h%2FsUA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D63">
-        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-software-engineer-remote-at-nexus-consulting-4382951509?position=8&amp;pageNum=0&amp;refId=oKF%2BMXc2c3k2gFDMYEDGXw%3D%3D&amp;trackingId=8ZP9GwniyepDC7nKLkWG6w%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/full-stack-developer-react-js-node-js-at-e2logy-software-solutions-4379171718?position=9&amp;pageNum=0&amp;refId=%2BRvL2ZGxx1ioN5%2Fos2VrJA%3D%3D&amp;trackingId=IfqTn1X7g3N25cs%2BLE8cxQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="D64">
-        <f>HYPERLINK("https://mx.linkedin.com/jobs/view/frontend-engineer-remote-at-north-star-staffing-4382955349?position=10&amp;pageNum=0&amp;refId=oKF%2BMXc2c3k2gFDMYEDGXw%3D%3D&amp;trackingId=frUUvZnZ2MeVCFKt1VEVXg%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://ca.linkedin.com/jobs/view/frontend-software-engineer-remote-at-nexus-consulting-4382951509?position=7&amp;pageNum=0&amp;refId=h4r43Urvsn15JJnftyN8uw%3D%3D&amp;trackingId=hjSRRANlTQWrz8wPXEc6Aw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D65">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-software-engineer-remote-at-quik-hire-staffing-4382936312?position=6&amp;pageNum=0&amp;refId=TYNRu%2Bgu7rglwiuCLIWVXg%3D%3D&amp;trackingId=SHDvC2KTuNBP%2FfRaLtvZlQ%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://mx.linkedin.com/jobs/view/frontend-engineer-remote-at-north-star-staffing-4382955349?position=10&amp;pageNum=0&amp;refId=h4r43Urvsn15JJnftyN8uw%3D%3D&amp;trackingId=%2FQwTFhCcVxj79%2FDlYDmFRw%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
         <v>99</v>
@@ -1915,16 +1918,16 @@
         <v>111</v>
       </c>
       <c r="D66">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-wireframe-at-ubique-systems-4381701450?position=4&amp;pageNum=0&amp;refId=pA9%2FT5aW3z3kdC5hqLV2OQ%3D%3D&amp;trackingId=VbPcNdOFN3DN9GKvg7GgPw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/frontend-software-engineer-remote-at-quik-hire-staffing-4382936312?position=7&amp;pageNum=0&amp;refId=jDDoTSDSYVb5DSoyfIwJTg%3D%3D&amp;trackingId=QtNb3NpI1EYV7QGvmZA%2BaQ%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
         <v>100</v>
@@ -1933,29 +1936,47 @@
         <v>113</v>
       </c>
       <c r="D67">
-        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-vue-js-at-tanla-platforms-limited-4379658046?position=2&amp;pageNum=0&amp;refId=gphOE8eHKsQK9tne%2BCXVMA%3D%3D&amp;trackingId=o1brmaMs4MXkKUE3Si15Dw%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-wireframe-at-ubique-systems-4381701450?position=4&amp;pageNum=0&amp;refId=s4laZP2P8eGZpEB5FiHh0g%3D%3D&amp;trackingId=PwFMkUXBoQAlAmvN9WFfNA%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
         <v>101</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D68">
-        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-full-stack-developer-php-javascript-m-w-d-at-finment-4381716039?position=4&amp;pageNum=0&amp;refId=6YubguW%2BTNJoyia5%2B8sJTQ%3D%3D&amp;trackingId=KnwmbE77ZqrEELh81J5fQA%3D%3D","Open Job")</f>
+        <f>HYPERLINK("https://in.linkedin.com/jobs/view/frontend-developer-vue-js-at-tanla-platforms-limited-4379658046?position=2&amp;pageNum=0&amp;refId=ADu0LbsGkzssEwYbc1PsZg%3D%3D&amp;trackingId=JHqm3XTpfTjbr%2BaTYoDE4w%3D%3D","Open Job")</f>
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>46</v>
+      </c>
+      <c r="B69" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69">
+        <f>HYPERLINK("https://de.linkedin.com/jobs/view/junior-full-stack-developer-php-javascript-m-w-d-at-finment-4381716039?position=4&amp;pageNum=0&amp;refId=%2Bc59cXFYWYY8Ch%2FbllFmhQ%3D%3D&amp;trackingId=oQ41XE37ecD6eNBpbN%2FQjA%3D%3D","Open Job")</f>
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
